--- a/MATH/M06/bus123-math-m06-l01-starter.xlsx
+++ b/MATH/M06/bus123-math-m06-l01-starter.xlsx
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -228,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -311,6 +312,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -386,6 +414,166 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="D6" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 10</t>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 210</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 10</t>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 230</t>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0">
+      <text>
+        <t>Build an Excel formula here that references the given cells in columns D:G.</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 10</t>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 210</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 230</t>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 250</t>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0">
+      <text>
+        <t>Build an Excel formula here that references the given cells in columns D:G.</t>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 20</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 230</t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <t>Build an Excel formula here that references the given cells in columns D:G.</t>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 12400</t>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 38600</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 9800</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <t>Build an Excel formula here that references the given cells in columns D:G.</t>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 80</t>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 48</t>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="0" shapeId="0">
+      <text>
+        <t>Build an Excel formula here that references the given cells in columns D:G.</t>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 80</t>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 48</t>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0">
+      <text>
+        <t>Build an Excel formula here that references the given cells in columns D:G.</t>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 9000</t>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 2400</t>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 4000</t>
+      </text>
+    </comment>
+    <comment ref="H12" authorId="0" shapeId="0">
+      <text>
+        <t>Build an Excel formula here that references the given cells in columns D:G.</t>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 22000</t>
+      </text>
+    </comment>
+    <comment ref="E13" authorId="0" shapeId="0">
+      <text>
+        <t>Type the slide given here: 110000</t>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0" shapeId="0">
+      <text>
+        <t>Build an Excel formula here that references the given cells in columns D:G.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -750,7 +938,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Open this tab during slide pauses. Use the exact numbers from the worked examples and let the feedback cell coach you.</t>
+          <t>Open this tab during slide pauses. Type the slide givens into the input cells first, then build formulas that reference those cells and let the feedback coach you.</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -920,17 +1108,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -943,15 +1132,15 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Self-graded Excel pauses using the exact numbers from the slides.</t>
+          <t>Self-graded Excel pauses: type the slide givens first, then build formulas that reference those input cells.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="34" customHeight="1">
       <c r="B4" s="29" t="inlineStr">
         <is>
-          <t>Enter your setup/work, type the final answer, then read the hint or feedback.</t>
+          <t>Use the exact slide numbers. Leave the given cells blank until class, then type them from the slide and build your formula in column H.</t>
         </is>
       </c>
       <c r="C4" s="27" t="n"/>
@@ -960,6 +1149,7 @@
       <c r="F4" s="27" t="n"/>
       <c r="G4" s="27" t="n"/>
       <c r="H4" s="27" t="n"/>
+      <c r="I4" s="27" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="B5" s="7" t="inlineStr">
@@ -974,298 +1164,217 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Scenario using slide numbers</t>
+          <t>Given 1</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>What to build</t>
+          <t>Given 2</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Final answer</t>
+          <t>Given 3</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Hint</t>
+          <t>Given 4</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
+          <t>Formula answer</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
           <t>Feedback</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="B6" s="8" t="n">
+    <row r="6" ht="45" customHeight="1">
+      <c r="B6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Inventory methods</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>FIFO COGS: 10 boards at $210 and 10 boards at $230 from the slide comparison.</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>Build the FIFO COGS formula.</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Use the oldest layers first: 10 x $210 plus 10 x $230.</t>
-        </is>
-      </c>
-      <c r="H6" s="18">
-        <f>IF(F6="","Hint: Use the oldest layers first: 10 x $210 plus 10 x $230.",IF(ABS(F6-4400)&lt;0.01,"Correct - self-check complete","Try again - Use the oldest layers first: 10 x $210 plus 10 x $230."))</f>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Inventory methods — FIFO COGS: D6 units from the $210 layer, E6 cost; F6 units from the $230 layer, G6 cost.</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="38" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="38" t="n"/>
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="40">
+        <f>IF(COUNTBLANK(D6:G6)&gt;0,"Start here: Type the four slide givens in D6:G6, then multiply units by unit cost for each layer.",IF(H6="","Next: build a formula in H6 that references your given cells.",IF(AND(AND(ABS(D6-10)&lt;0.01,ABS(E6-210)&lt;0.01,ABS(F6-10)&lt;0.01,ABS(G6-230)&lt;0.01),ABS(H6-(D6*E6+F6*G6))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="B7" s="10" t="n">
+    <row r="7" ht="45" customHeight="1">
+      <c r="B7" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Inventory methods</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>WAC unit cost: 10 boards each at $210, $230, and $250.</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>Find the blended unit cost.</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="n"/>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>Add the three layer costs, then divide by 30 total units.</t>
-        </is>
-      </c>
-      <c r="H7" s="18">
-        <f>IF(F7="","Hint: Add the three layer costs, then divide by 30 total units.",IF(ABS(F7-230)&lt;0.01,"Correct - self-check complete","Try again - Add the three layer costs, then divide by 30 total units."))</f>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Inventory methods — WAC unit cost: D7 units per layer; E7, F7, and G7 are the three layer costs.</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="38" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="38" t="n"/>
+      <c r="H7" s="38" t="n"/>
+      <c r="I7" s="40">
+        <f>IF(COUNTBLANK(D7:G7)&gt;0,"Start here: Type the layer givens in D7:G7, then divide total cost by total units.",IF(H7="","Next: build a formula in H7 that references your given cells.",IF(AND(AND(ABS(D7-10)&lt;0.01,ABS(E7-210)&lt;0.01,ABS(F7-230)&lt;0.01,ABS(G7-250)&lt;0.01),ABS(H7-((D7*E7+D7*F7+D7*G7)/(D7*3)))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="B8" s="8" t="n">
+    <row r="8" ht="45" customHeight="1">
+      <c r="B8" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Inventory methods</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>WAC COGS: 20 units sold using the $230.00 weighted-average unit cost.</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>Multiply units sold by WAC unit cost.</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Use 20 units sold times the weighted-average cost.</t>
-        </is>
-      </c>
-      <c r="H8" s="18">
-        <f>IF(F8="","Hint: Use 20 units sold times the weighted-average cost.",IF(ABS(F8-4600)&lt;0.01,"Correct - self-check complete","Try again - Use 20 units sold times the weighted-average cost."))</f>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>Inventory methods — WAC COGS: D8 units sold; E8 weighted-average unit cost from the slide.</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="41" t="n"/>
+      <c r="G8" s="41" t="n"/>
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="40">
+        <f>IF(COUNTBLANK(D8:E8)&gt;0,"Start here: Type units sold and the WAC unit cost first, then multiply those cells.",IF(H8="","Next: build a formula in H8 that references your given cells.",IF(AND(AND(ABS(D8-20)&lt;0.01,ABS(E8-230)&lt;0.01),ABS(H8-(D8*E8))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="B9" s="10" t="n">
+    <row r="9" ht="45" customHeight="1">
+      <c r="B9" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>COGS schedule</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Beginning inventory $12,400, purchases $38,600, ending inventory $9,800.</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>Calculate COGS.</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>Beginning inventory + purchases - ending inventory.</t>
-        </is>
-      </c>
-      <c r="H9" s="18">
-        <f>IF(F9="","Hint: Beginning inventory + purchases - ending inventory.",IF(ABS(F9-41200)&lt;0.01,"Correct - self-check complete","Try again - Beginning inventory + purchases - ending inventory."))</f>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>COGS schedule — COGS schedule: D9 beginning inventory; E9 purchases; F9 ending inventory.</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="41" t="n"/>
+      <c r="H9" s="39" t="n"/>
+      <c r="I9" s="40">
+        <f>IF(COUNTBLANK(D9:F9)&gt;0,"Start here: Type the three schedule givens first, then subtract ending inventory.",IF(H9="","Next: build a formula in H9 that references your given cells.",IF(AND(AND(ABS(D9-12400)&lt;0.01,ABS(E9-38600)&lt;0.01,ABS(F9-9800)&lt;0.01),ABS(H9-(D9+E9-F9))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="B10" s="8" t="n">
+    <row r="10" ht="45" customHeight="1">
+      <c r="B10" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Margin vs. markup</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Surf bag sells for $80 and costs Tidal $48.</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>Calculate gross margin percent.</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>Profit is $32. Margin divides profit by revenue.</t>
-        </is>
-      </c>
-      <c r="H10" s="18">
-        <f>IF(F10="","Hint: Profit is $32. Margin divides profit by revenue.",IF(OR(ABS(F10-0.4)&lt;0.001,ABS(F10-40.0)&lt;0.1),"Correct - self-check complete","Try again - Profit is $32. Margin divides profit by revenue."))</f>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>Margin vs. markup — Gross margin: D10 selling price; E10 cost.</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="41" t="n"/>
+      <c r="G10" s="41" t="n"/>
+      <c r="H10" s="42" t="n"/>
+      <c r="I10" s="40">
+        <f>IF(COUNTBLANK(D10:E10)&gt;0,"Start here: Type price and cost, then divide profit by the selling price cell.",IF(H10="","Next: build a formula in H10 that references your given cells.",IF(AND(AND(ABS(D10-80)&lt;0.01,ABS(E10-48)&lt;0.01),ABS(H10-((D10-E10)/D10))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="B11" s="10" t="n">
+    <row r="11" ht="45" customHeight="1">
+      <c r="B11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Margin vs. markup</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Surf bag sells for $80 and costs Tidal $48.</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>Calculate markup percent.</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>Profit is $32. Markup divides profit by cost.</t>
-        </is>
-      </c>
-      <c r="H11" s="18">
-        <f>IF(F11="","Hint: Profit is $32. Markup divides profit by cost.",IF(OR(ABS(F11-0.6666666666666666)&lt;0.001,ABS(F11-66.66666666666666)&lt;0.1),"Correct - self-check complete","Try again - Profit is $32. Markup divides profit by cost."))</f>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>Margin vs. markup — Markup: D11 selling price; E11 cost.</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="41" t="n"/>
+      <c r="G11" s="41" t="n"/>
+      <c r="H11" s="42" t="n"/>
+      <c r="I11" s="40">
+        <f>IF(COUNTBLANK(D11:E11)&gt;0,"Start here: Type price and cost, then divide profit by the cost cell.",IF(H11="","Next: build a formula in H11 that references your given cells.",IF(AND(AND(ABS(D11-80)&lt;0.01,ABS(E11-48)&lt;0.01),ABS(H11-((D11-E11)/E11))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="B12" s="8" t="n">
+    <row r="12" ht="45" customHeight="1">
+      <c r="B12" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Overhead allocation</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Monthly rent $9,000. Surf Shop is 2,400 sq ft out of 4,000 total sq ft.</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>Allocate rent to the Surf Shop.</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>First find the 60% space share, then multiply by rent.</t>
-        </is>
-      </c>
-      <c r="H12" s="18">
-        <f>IF(F12="","Hint: First find the 60% space share, then multiply by rent.",IF(ABS(F12-5400)&lt;0.01,"Correct - self-check complete","Try again - First find the 60% space share, then multiply by rent."))</f>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>Overhead allocation — Rent allocation: D12 rent; E12 Surf Shop sq ft; F12 total sq ft.</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="41" t="n"/>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="40">
+        <f>IF(COUNTBLANK(D12:F12)&gt;0,"Start here: Type rent and square footage, then multiply rent by the space share.",IF(H12="","Next: build a formula in H12 that references your given cells.",IF(AND(AND(ABS(D12-9000)&lt;0.01,ABS(E12-2400)&lt;0.01,ABS(F12-4000)&lt;0.01),ABS(H12-(D12*(E12/F12)))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="B13" s="10" t="n">
+    <row r="13" ht="45" customHeight="1">
+      <c r="B13" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Overhead rate</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Total overhead $22,000 and revenue $110,000.</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>Calculate the overhead rate.</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>Overhead rate = total overhead divided by revenue.</t>
-        </is>
-      </c>
-      <c r="H13" s="18">
-        <f>IF(F13="","Hint: Overhead rate = total overhead divided by revenue.",IF(OR(ABS(F13-0.2)&lt;0.001,ABS(F13-20.0)&lt;0.1),"Correct - self-check complete","Try again - Overhead rate = total overhead divided by revenue."))</f>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>Overhead rate — Overhead rate: D13 total overhead; E13 revenue.</t>
+        </is>
+      </c>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="41" t="n"/>
+      <c r="G13" s="41" t="n"/>
+      <c r="H13" s="42" t="n"/>
+      <c r="I13" s="40">
+        <f>IF(COUNTBLANK(D13:E13)&gt;0,"Start here: Type overhead and revenue, then divide overhead by revenue.",IF(H13="","Next: build a formula in H13 that references your given cells.",IF(AND(AND(ABS(D13-22000)&lt;0.01,ABS(E13-110000)&lt;0.01),ABS(H13-(D13/E13))&lt;0.01),"Correct - self-check complete","Check the typed givens and formula math.")))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1"/>
     <row r="15" ht="22" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="26" customHeight="1">
       <c r="B16" s="31" t="inlineStr">
         <is>
           <t>Self-check score</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n"/>
+      <c r="C16" s="28" t="n"/>
       <c r="D16" s="33">
-        <f>COUNTIF(H6:H13,"Correct*")&amp;" of 8 complete"</f>
+        <f>COUNTIF(I6:I13,"Correct*")&amp;" of 8 complete"</f>
         <v/>
       </c>
-      <c r="E16" s="23" t="n"/>
-      <c r="F16" s="23" t="n"/>
-      <c r="G16" s="23" t="n"/>
-      <c r="H16" s="23" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="27" t="n"/>
+      <c r="I16" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1834,7 +1943,7 @@
           <t>COGS</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>=BeginningInventory+Purchases-EndingInventory</t>
         </is>
@@ -1856,7 +1965,7 @@
           <t>Goods available for sale</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>=BeginningInventory+Purchases</t>
         </is>
@@ -1878,7 +1987,7 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>=Revenue-COGS</t>
         </is>
@@ -1900,7 +2009,7 @@
           <t>Gross margin percent</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>=GrossProfit/Revenue</t>
         </is>
@@ -1922,7 +2031,7 @@
           <t>Markup percent</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>=(Revenue-Cost)/Cost</t>
         </is>
@@ -1944,7 +2053,7 @@
           <t>WAC unit cost</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>=TotalCostAvailable/TotalUnitsAvailable</t>
         </is>
@@ -1966,7 +2075,7 @@
           <t>Overhead allocated</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>=TotalOverhead*DeptPercent</t>
         </is>
@@ -1988,7 +2097,7 @@
           <t>Overhead rate</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>=TotalOverhead/Revenue</t>
         </is>
